--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Sherwin_2022_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Sherwin_2022_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{B84FD12B-CCB6-0543-A95D-92C612F77944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D21CA660-74B3-4DE0-9843-8378FB94577A}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -1044,7 +1044,7 @@
         </row>
         <row r="19">
           <cell r="C19">
-            <v>0.8</v>
+            <v>1.7</v>
           </cell>
         </row>
         <row r="21">
@@ -1089,12 +1089,12 @@
         </row>
         <row r="33">
           <cell r="C33">
-            <v>1282</v>
+            <v>1371</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>480</v>
+            <v>523</v>
           </cell>
         </row>
       </sheetData>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C18" s="48">
         <f>[1]Inputs!C19</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="C32" s="48">
         <f>[1]Inputs!C33</f>
-        <v>1282</v>
+        <v>1371</v>
       </c>
       <c r="D32" t="s">
         <v>29</v>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="C33" s="48">
         <f>[1]Inputs!C34</f>
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="D106" s="21">
         <f>Inputs!$C$32</f>
-        <v>1282</v>
+        <v>1371</v>
       </c>
       <c r="E106" s="21">
         <v>473.00611961462351</v>
@@ -4568,11 +4568,11 @@
       </c>
       <c r="G106" s="21">
         <f>Inputs!$C$33</f>
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="H106" s="21">
         <f>Inputs!$C$33</f>
-        <v>480</v>
+        <v>523</v>
       </c>
     </row>
     <row r="107" spans="2:15">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="D114" s="5">
         <f>D89/D105*D106</f>
-        <v>1.6354046666666666</v>
+        <v>1.748939</v>
       </c>
       <c r="E114" s="5">
         <f>E89/E105*E106</f>
@@ -4700,11 +4700,11 @@
       </c>
       <c r="G114" s="5">
         <f>G89/G105*G106</f>
-        <v>0.59224615384615376</v>
+        <v>0.64530153846153837</v>
       </c>
       <c r="H114" s="5">
         <f>H89/H105*H106</f>
-        <v>1.0608</v>
+        <v>1.1558300000000001</v>
       </c>
       <c r="I114" t="s">
         <v>21</v>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="D115" s="5">
         <f>D102/D105*D106</f>
-        <v>1.6119013333333332</v>
+        <v>1.7238039999999999</v>
       </c>
       <c r="E115" s="5">
         <f>E102/E105*E106</f>
@@ -4728,11 +4728,11 @@
       </c>
       <c r="G115" s="5">
         <f>G102/G105*G106</f>
-        <v>0.11748923076923076</v>
+        <v>0.12801430769230768</v>
       </c>
       <c r="H115" s="5">
         <f>H102/H105*H106</f>
-        <v>4.8144000000000006E-2</v>
+        <v>5.2456900000000008E-2</v>
       </c>
       <c r="I115" t="s">
         <v>21</v>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="D121" s="5">
         <f>D103+(D114-D89)+(D115-D102)+(D116-D80)</f>
-        <v>7.1184803589743595</v>
+        <v>7.3439173589743589</v>
       </c>
       <c r="E121" s="5">
         <f>E103+(E114-E89)+(E115-E102)+(E116-E80)</f>
@@ -4841,11 +4841,11 @@
       </c>
       <c r="G121" s="5">
         <f>G103+(G114-G89)+(G115-G102)+(G116-G80)</f>
-        <v>1.4505221642764017</v>
+        <v>1.5141026258148629</v>
       </c>
       <c r="H121" s="29">
         <f>H103+(H114-H89)+(H115-H102)+(H116-H80)</f>
-        <v>1.8130411186440678</v>
+        <v>1.9123840186440677</v>
       </c>
     </row>
     <row r="122" spans="2:15" ht="17.100000000000001" customHeight="1" thickBot="1">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="D122" s="32">
         <f>D103*D118+(D114-D89)+(D115-D102)+(D116-D80)</f>
-        <v>6.3245734390500221</v>
+        <v>6.5500104390500216</v>
       </c>
       <c r="E122" s="32">
         <f>E103*E118+(E114-E89)+(E115-E102)+(E116-E80)</f>
@@ -4869,11 +4869,11 @@
       </c>
       <c r="G122" s="32">
         <f>G103*G118+(G114-G89)+(G115-G102)+(G116-G80)</f>
-        <v>1.5586494341376875</v>
+        <v>1.6222298956761492</v>
       </c>
       <c r="H122" s="33">
         <f>H103*H118+(H114-H89)+(H115-H102)+(H116-H80)</f>
-        <v>1.9212252138521382</v>
+        <v>2.0205681138521387</v>
       </c>
     </row>
     <row r="125" spans="2:15">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="D152" s="21">
         <f>Inputs!$C$32</f>
-        <v>1282</v>
+        <v>1371</v>
       </c>
       <c r="E152" s="21">
         <v>473.00611961462351</v>
@@ -5611,11 +5611,11 @@
       </c>
       <c r="G152" s="21">
         <f>Inputs!$C$33</f>
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="H152" s="21">
         <f>Inputs!$C$33</f>
-        <v>480</v>
+        <v>523</v>
       </c>
     </row>
     <row r="154" spans="2:8">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="D160" s="5">
         <f>D135/D151*D152</f>
-        <v>1.6354046666666666</v>
+        <v>1.748939</v>
       </c>
       <c r="E160" s="5">
         <f>E135/E151*E152</f>
@@ -5731,11 +5731,11 @@
       </c>
       <c r="G160" s="5">
         <f>G135/G151*G152</f>
-        <v>0.61476923076923085</v>
+        <v>0.66984230769230779</v>
       </c>
       <c r="H160" s="5">
         <f>H135/H151*H152</f>
-        <v>1.08768</v>
+        <v>1.1851179999999999</v>
       </c>
     </row>
     <row r="161" spans="2:9">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="D161" s="5">
         <f>D148/D151*D152</f>
-        <v>2.0116716666666665</v>
+        <v>2.1513274999999998</v>
       </c>
       <c r="E161" s="5">
         <f>E148/E151*E152</f>
@@ -5756,11 +5756,11 @@
       </c>
       <c r="G161" s="5">
         <f>G148/G151*G152</f>
-        <v>0.22918153846153846</v>
+        <v>0.24971238461538461</v>
       </c>
       <c r="H161" s="5">
         <f>H148/H151*H152</f>
-        <v>5.7071999999999998E-2</v>
+        <v>6.2184699999999996E-2</v>
       </c>
     </row>
     <row r="162" spans="2:9">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D167" s="5">
         <f>D149+(D160-D135)+(D161-D148)+(D162-D126)</f>
-        <v>7.0685842935323375</v>
+        <v>7.3217744601990056</v>
       </c>
       <c r="E167" s="5">
         <f>E149+(E160-E135)+(E161-E148)+(E162-E126)</f>
@@ -5863,11 +5863,11 @@
       </c>
       <c r="G167" s="5">
         <f>G149+(G160-G135)+(G161-G148)+(G162-G126)</f>
-        <v>1.4497334008097167</v>
+        <v>1.5253373238866399</v>
       </c>
       <c r="H167" s="29">
         <f>H149+(H160-H135)+(H161-H148)+(H162-H126)</f>
-        <v>1.7376672631578947</v>
+        <v>1.8402179631578945</v>
       </c>
     </row>
     <row r="168" spans="2:9" ht="17.100000000000001" customHeight="1" thickBot="1">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="D168" s="32">
         <f>D149*D164+(D160-D135)+(D161-D148)+(D162-D126)</f>
-        <v>6.3159325753734485</v>
+        <v>6.5691227420401148</v>
       </c>
       <c r="E168" s="32">
         <f>E149*E164+(E160-E135)+(E161-E148)+(E162-E126)</f>
@@ -5891,11 +5891,11 @@
       </c>
       <c r="G168" s="32">
         <f>G149*G164+(G160-G135)+(G161-G148)+(G162-G126)</f>
-        <v>1.5619861908475476</v>
+        <v>1.6375901139244708</v>
       </c>
       <c r="H168" s="33">
         <f>H149*H164+(H160-H135)+(H161-H148)+(H162-H126)</f>
-        <v>1.8492836093117409</v>
+        <v>1.9518343093117405</v>
       </c>
     </row>
     <row r="170" spans="2:9">
@@ -5966,11 +5966,11 @@
       </c>
       <c r="G173" s="21">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="H173" s="21">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="I173" t="s">
         <v>155</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="D182" s="4">
         <f>(D121-$C$173)/$C$172*1000</f>
-        <v>2461.2655850815854</v>
+        <v>2543.2426759906762</v>
       </c>
       <c r="E182" s="4">
         <f>(E121-$C$173)/$C$172*1000</f>
@@ -6130,11 +6130,11 @@
       </c>
       <c r="G182" s="4">
         <f>(G121-$C$173)/$C$172*1000</f>
-        <v>400.18987791869148</v>
+        <v>423.31004575085916</v>
       </c>
       <c r="H182" s="38">
         <f>(H121-$C$173)/$C$172*1000</f>
-        <v>532.01495223420648</v>
+        <v>568.13964314329735</v>
       </c>
     </row>
     <row r="183" spans="2:8">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D183" s="4">
         <f>(D167-$C$173)/$C$172*1000</f>
-        <v>2443.1215612844867</v>
+        <v>2535.1907127996383</v>
       </c>
       <c r="E183" s="4">
         <f>(E167-$C$173)/$C$172*1000</f>
@@ -6156,11 +6156,11 @@
       </c>
       <c r="G183" s="4">
         <f>(G167-$C$173)/$C$172*1000</f>
-        <v>399.90305483989698</v>
+        <v>427.39539050423275</v>
       </c>
       <c r="H183" s="38">
         <f>(H167-$C$173)/$C$172*1000</f>
-        <v>504.60627751196165</v>
+        <v>541.89744114832536</v>
       </c>
     </row>
     <row r="184" spans="2:8">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="D184" s="4">
         <f>(D122-$C$173)/$C$172*1000</f>
-        <v>2172.5721596545536</v>
+        <v>2254.5492505636444</v>
       </c>
       <c r="E184" s="4">
         <f>(E122-$C$173)/$C$172*1000</f>
@@ -6184,11 +6184,11 @@
       </c>
       <c r="G184" s="4">
         <f>(G122-$C$173)/$C$172*1000</f>
-        <v>439.50888514097727</v>
+        <v>462.62905297314512</v>
       </c>
       <c r="H184" s="38">
         <f>(H122-$C$173)/$C$172*1000</f>
-        <v>571.35462321895932</v>
+        <v>607.47931412805042</v>
       </c>
     </row>
     <row r="185" spans="2:8">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="D185" s="4">
         <f>(D168-$C$173)/$C$172*1000</f>
-        <v>2169.4300274085267</v>
+        <v>2261.4991789236783</v>
       </c>
       <c r="E185" s="4">
         <f>(E168-$C$173)/$C$172*1000</f>
@@ -6210,11 +6210,11 @@
       </c>
       <c r="G185" s="4">
         <f>(G168-$C$173)/$C$172*1000</f>
-        <v>440.72225121729002</v>
+        <v>468.21458688162579</v>
       </c>
       <c r="H185" s="38">
         <f>(H168-$C$173)/$C$172*1000</f>
-        <v>545.19403974972397</v>
+        <v>582.48520338608739</v>
       </c>
     </row>
     <row r="186" spans="2:8">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="D186" s="4">
         <f>(D122-D$173)/$C$172*1000</f>
-        <v>2008.9357960181896</v>
+        <v>2090.9128869272809</v>
       </c>
       <c r="E186" s="4">
         <f>(E122-E$173)/$C$172*1000</f>
@@ -6238,11 +6238,11 @@
       </c>
       <c r="G186" s="4">
         <f>(G122-G$173)/$C$172*1000</f>
-        <v>275.87252150461359</v>
+        <v>-28.280037935945742</v>
       </c>
       <c r="H186" s="38">
         <f>(H122-H$173)/$C$172*1000</f>
-        <v>407.71825958259569</v>
+        <v>116.57022321895955</v>
       </c>
     </row>
     <row r="187" spans="2:8">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="D187" s="4">
         <f>(D168-D$173)/$C$172*1000</f>
-        <v>2005.7936637721632</v>
+        <v>2097.8628152873148</v>
       </c>
       <c r="E187" s="4">
         <f>(E168-E$173)/$C$172*1000</f>
@@ -6264,11 +6264,11 @@
       </c>
       <c r="G187" s="4">
         <f>(G168-G$173)/$C$172*1000</f>
-        <v>277.0858875809264</v>
+        <v>-22.694504027465133</v>
       </c>
       <c r="H187" s="38">
         <f>(H168-H$173)/$C$172*1000</f>
-        <v>381.55767611336029</v>
+        <v>91.57611247699657</v>
       </c>
     </row>
     <row r="188" spans="2:8">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="D188" s="7">
         <f>(D122-D$173)/$D$172*1000</f>
-        <v>1795.4604340607475</v>
+        <v>1868.7264008071234</v>
       </c>
       <c r="E188" s="7">
         <f>(E122-E$173)/$D$172*1000</f>
@@ -6292,11 +6292,11 @@
       </c>
       <c r="G188" s="7">
         <f>(G122-G$173)/$D$172*1000</f>
-        <v>246.55750481814877</v>
+        <v>-25.274918834323856</v>
       </c>
       <c r="H188" s="40">
         <f>(H122-H$173)/$D$172*1000</f>
-        <v>364.39293121044642</v>
+        <v>104.18313218078387</v>
       </c>
     </row>
     <row r="189" spans="2:8" ht="17.100000000000001" customHeight="1" thickBot="1">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="D189" s="42">
         <f>(D168-D$173)/$D$172*1000</f>
-        <v>1792.6521939280813</v>
+        <v>1874.9378095613156</v>
       </c>
       <c r="E189" s="42">
         <f>(E168-E$173)/$D$172*1000</f>
@@ -6318,11 +6318,11 @@
       </c>
       <c r="G189" s="42">
         <f>(G168-G$173)/$D$172*1000</f>
-        <v>247.64193508534254</v>
+        <v>-20.282920008050358</v>
       </c>
       <c r="H189" s="43">
         <f>(H168-H$173)/$D$172*1000</f>
-        <v>341.01224744541361</v>
+        <v>81.844968357592705</v>
       </c>
     </row>
     <row r="190" spans="2:8" ht="17.100000000000001" customHeight="1" thickBot="1">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D195" s="4">
         <f>(D121-$C$174)/$C$172*1000</f>
-        <v>2293.9928578088579</v>
+        <v>2375.9699487179487</v>
       </c>
       <c r="E195" s="4">
         <f>(E121-$C$174)/$C$172*1000</f>
@@ -6463,11 +6463,11 @@
       </c>
       <c r="G195" s="4">
         <f>(G121-$C$174)/$C$172*1000</f>
-        <v>232.91715064596423</v>
+        <v>256.03731847813197</v>
       </c>
       <c r="H195" s="38">
         <f>(H121-$C$174)/$C$172*1000</f>
-        <v>364.74222496147917</v>
+        <v>400.86691587057004</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="D196" s="4">
         <f>(D167-$C$174)/$C$172*1000</f>
-        <v>2275.8488340117592</v>
+        <v>2367.9179855269108</v>
       </c>
       <c r="E196" s="4">
         <f>(E167-$C$174)/$C$172*1000</f>
@@ -6489,11 +6489,11 @@
       </c>
       <c r="G196" s="4">
         <f>(G167-$C$174)/$C$172*1000</f>
-        <v>232.6303275671697</v>
+        <v>260.12266323150538</v>
       </c>
       <c r="H196" s="38">
         <f>(H167-$C$174)/$C$172*1000</f>
-        <v>337.3335502392344</v>
+        <v>374.62471387559799</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="D197" s="4">
         <f>(D122-$C$174)/$C$172*1000</f>
-        <v>2005.2994323818259</v>
+        <v>2087.2765232909169</v>
       </c>
       <c r="E197" s="4">
         <f>(E122-$C$174)/$C$172*1000</f>
@@ -6517,11 +6517,11 @@
       </c>
       <c r="G197" s="4">
         <f>(G122-$C$174)/$C$172*1000</f>
-        <v>272.23615786825002</v>
+        <v>295.35632570041787</v>
       </c>
       <c r="H197" s="38">
         <f>(H122-$C$174)/$C$172*1000</f>
-        <v>404.08189594623207</v>
+        <v>440.20658685532317</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="D198" s="4">
         <f>(D168-$C$174)/$C$172*1000</f>
-        <v>2002.1573001357992</v>
+        <v>2094.2264516509508</v>
       </c>
       <c r="E198" s="4">
         <f>(E168-$C$174)/$C$172*1000</f>
@@ -6543,11 +6543,11 @@
       </c>
       <c r="G198" s="4">
         <f>(G168-$C$174)/$C$172*1000</f>
-        <v>273.44952394456271</v>
+        <v>300.94185960889848</v>
       </c>
       <c r="H198" s="38">
         <f>(H168-$C$174)/$C$172*1000</f>
-        <v>377.92131247699666</v>
+        <v>415.21247611336014</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="D199" s="4">
         <f>(D122-D$173)/$C$172*1000</f>
-        <v>2008.9357960181896</v>
+        <v>2090.9128869272809</v>
       </c>
       <c r="E199" s="4">
         <f>(E122-E$173)/$C$172*1000</f>
@@ -6571,11 +6571,11 @@
       </c>
       <c r="G199" s="4">
         <f>(G122-G$173)/$C$172*1000</f>
-        <v>275.87252150461359</v>
+        <v>-28.280037935945742</v>
       </c>
       <c r="H199" s="38">
         <f>(H122-H$173)/$C$172*1000</f>
-        <v>407.71825958259569</v>
+        <v>116.57022321895955</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="D200" s="4">
         <f>(D168-D$173)/$C$172*1000</f>
-        <v>2005.7936637721632</v>
+        <v>2097.8628152873148</v>
       </c>
       <c r="E200" s="4">
         <f>(E168-E$173)/$C$172*1000</f>
@@ -6597,11 +6597,11 @@
       </c>
       <c r="G200" s="4">
         <f>(G168-G$173)/$C$172*1000</f>
-        <v>277.0858875809264</v>
+        <v>-22.694504027465133</v>
       </c>
       <c r="H200" s="38">
         <f>(H168-H$173)/$C$172*1000</f>
-        <v>381.55767611336029</v>
+        <v>91.57611247699657</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="D201" s="7">
         <f>(D122-D$173)/$D$172*1000</f>
-        <v>1795.4604340607475</v>
+        <v>1868.7264008071234</v>
       </c>
       <c r="E201" s="7">
         <f>(E122-E$173)/$D$172*1000</f>
@@ -6625,11 +6625,11 @@
       </c>
       <c r="G201" s="7">
         <f>(G122-G$173)/$D$172*1000</f>
-        <v>246.55750481814877</v>
+        <v>-25.274918834323856</v>
       </c>
       <c r="H201" s="40">
         <f>(H122-H$173)/$D$172*1000</f>
-        <v>364.39293121044642</v>
+        <v>104.18313218078387</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="17.100000000000001" customHeight="1" thickBot="1">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="D202" s="42">
         <f>(D168-D$173)/$D$172*1000</f>
-        <v>1792.6521939280813</v>
+        <v>1874.9378095613156</v>
       </c>
       <c r="E202" s="42">
         <f>(E168-E$173)/$D$172*1000</f>
@@ -6651,11 +6651,11 @@
       </c>
       <c r="G202" s="42">
         <f>(G168-G$173)/$D$172*1000</f>
-        <v>247.64193508534254</v>
+        <v>-20.282920008050358</v>
       </c>
       <c r="H202" s="43">
         <f>(H168-H$173)/$D$172*1000</f>
-        <v>341.01224744541361</v>
+        <v>81.844968357592705</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -6749,19 +6749,19 @@
       </c>
       <c r="E208" s="7">
         <f t="array" ref="E208">INDEX($D$178:$H$189,E$206,$A208)</f>
-        <v>2461.2655850815854</v>
+        <v>2543.2426759906762</v>
       </c>
       <c r="F208" s="7">
         <f t="array" ref="F208">INDEX($D$178:$H$189,F$206,$A208)</f>
-        <v>2172.5721596545536</v>
+        <v>2254.5492505636444</v>
       </c>
       <c r="G208" s="7">
         <f t="array" ref="G208">INDEX($D$178:$H$189,G$206,$A208)</f>
-        <v>2008.9357960181896</v>
+        <v>2090.9128869272809</v>
       </c>
       <c r="H208" s="7">
         <f t="array" ref="H208">INDEX($D$178:$H$189,H$206,$A208)</f>
-        <v>1795.4604340607475</v>
+        <v>1868.7264008071234</v>
       </c>
       <c r="I208" t="s">
         <v>166</v>
@@ -6854,19 +6854,19 @@
       </c>
       <c r="E211" s="7">
         <f t="array" ref="E211">INDEX($D$178:$H$189,E$206,$A211)</f>
-        <v>400.18987791869148</v>
+        <v>423.31004575085916</v>
       </c>
       <c r="F211" s="7">
         <f t="array" ref="F211">INDEX($D$178:$H$189,F$206,$A211)</f>
-        <v>439.50888514097727</v>
+        <v>462.62905297314512</v>
       </c>
       <c r="G211" s="7">
         <f t="array" ref="G211">INDEX($D$178:$H$189,G$206,$A211)</f>
-        <v>275.87252150461359</v>
+        <v>-28.280037935945742</v>
       </c>
       <c r="H211" s="7">
         <f t="array" ref="H211">INDEX($D$178:$H$189,H$206,$A211)</f>
-        <v>246.55750481814877</v>
+        <v>-25.274918834323856</v>
       </c>
       <c r="I211" t="s">
         <v>167</v>
@@ -6889,19 +6889,19 @@
       </c>
       <c r="E212" s="7">
         <f t="array" ref="E212">INDEX($D$178:$H$189,E$206,$A212)</f>
-        <v>532.01495223420648</v>
+        <v>568.13964314329735</v>
       </c>
       <c r="F212" s="7">
         <f t="array" ref="F212">INDEX($D$178:$H$189,F$206,$A212)</f>
-        <v>571.35462321895932</v>
+        <v>607.47931412805042</v>
       </c>
       <c r="G212" s="7">
         <f t="array" ref="G212">INDEX($D$178:$H$189,G$206,$A212)</f>
-        <v>407.71825958259569</v>
+        <v>116.57022321895955</v>
       </c>
       <c r="H212" s="7">
         <f t="array" ref="H212">INDEX($D$178:$H$189,H$206,$A212)</f>
-        <v>364.39293121044642</v>
+        <v>104.18313218078387</v>
       </c>
       <c r="I212" t="s">
         <v>166</v>
@@ -6956,19 +6956,19 @@
       </c>
       <c r="E216" s="7">
         <f t="array" ref="E216">INDEX($D$178:$H$189,E$214,$A216)</f>
-        <v>2443.1215612844867</v>
+        <v>2535.1907127996383</v>
       </c>
       <c r="F216" s="7">
         <f t="array" ref="F216">INDEX($D$178:$H$189,F$214,$A216)</f>
-        <v>2169.4300274085267</v>
+        <v>2261.4991789236783</v>
       </c>
       <c r="G216" s="7">
         <f t="array" ref="G216">INDEX($D$178:$H$189,G$214,$A216)</f>
-        <v>2005.7936637721632</v>
+        <v>2097.8628152873148</v>
       </c>
       <c r="H216" s="7">
         <f t="array" ref="H216">INDEX($D$178:$H$189,H$214,$A216)</f>
-        <v>1792.6521939280813</v>
+        <v>1874.9378095613156</v>
       </c>
       <c r="I216" t="s">
         <v>166</v>
@@ -7061,19 +7061,19 @@
       </c>
       <c r="E219" s="7">
         <f t="array" ref="E219">INDEX($D$178:$H$189,E$214,$A219)</f>
-        <v>399.90305483989698</v>
+        <v>427.39539050423275</v>
       </c>
       <c r="F219" s="7">
         <f t="array" ref="F219">INDEX($D$178:$H$189,F$214,$A219)</f>
-        <v>440.72225121729002</v>
+        <v>468.21458688162579</v>
       </c>
       <c r="G219" s="7">
         <f t="array" ref="G219">INDEX($D$178:$H$189,G$214,$A219)</f>
-        <v>277.0858875809264</v>
+        <v>-22.694504027465133</v>
       </c>
       <c r="H219" s="7">
         <f t="array" ref="H219">INDEX($D$178:$H$189,H$214,$A219)</f>
-        <v>247.64193508534254</v>
+        <v>-20.282920008050358</v>
       </c>
       <c r="I219" t="s">
         <v>167</v>
@@ -7096,19 +7096,19 @@
       </c>
       <c r="E220" s="7">
         <f t="array" ref="E220">INDEX($D$178:$H$189,E$214,$A220)</f>
-        <v>504.60627751196165</v>
+        <v>541.89744114832536</v>
       </c>
       <c r="F220" s="7">
         <f t="array" ref="F220">INDEX($D$178:$H$189,F$214,$A220)</f>
-        <v>545.19403974972397</v>
+        <v>582.48520338608739</v>
       </c>
       <c r="G220" s="7">
         <f t="array" ref="G220">INDEX($D$178:$H$189,G$214,$A220)</f>
-        <v>381.55767611336029</v>
+        <v>91.57611247699657</v>
       </c>
       <c r="H220" s="7">
         <f t="array" ref="H220">INDEX($D$178:$H$189,H$214,$A220)</f>
-        <v>341.01224744541361</v>
+        <v>81.844968357592705</v>
       </c>
       <c r="I220" t="s">
         <v>166</v>
@@ -7154,19 +7154,19 @@
       </c>
       <c r="E223" s="7">
         <f t="array" ref="E223">INDEX($D$191:$H$202,E$222,$A223)</f>
-        <v>2293.9928578088579</v>
+        <v>2375.9699487179487</v>
       </c>
       <c r="F223" s="7">
         <f t="array" ref="F223">INDEX($D$191:$H$202,F$222,$A223)</f>
-        <v>2005.2994323818259</v>
+        <v>2087.2765232909169</v>
       </c>
       <c r="G223" s="7">
         <f t="array" ref="G223">INDEX($D$191:$H$202,G$222,$A223)</f>
-        <v>2008.9357960181896</v>
+        <v>2090.9128869272809</v>
       </c>
       <c r="H223" s="7">
         <f t="array" ref="H223">INDEX($D$191:$H$202,H$222,$A223)</f>
-        <v>1795.4604340607475</v>
+        <v>1868.7264008071234</v>
       </c>
       <c r="I223" t="s">
         <v>166</v>
@@ -7259,19 +7259,19 @@
       </c>
       <c r="E226" s="7">
         <f t="array" ref="E226">INDEX($D$191:$H$202,E$222,$A226)</f>
-        <v>232.91715064596423</v>
+        <v>256.03731847813197</v>
       </c>
       <c r="F226" s="7">
         <f t="array" ref="F226">INDEX($D$191:$H$202,F$222,$A226)</f>
-        <v>272.23615786825002</v>
+        <v>295.35632570041787</v>
       </c>
       <c r="G226" s="7">
         <f t="array" ref="G226">INDEX($D$191:$H$202,G$222,$A226)</f>
-        <v>275.87252150461359</v>
+        <v>-28.280037935945742</v>
       </c>
       <c r="H226" s="7">
         <f t="array" ref="H226">INDEX($D$191:$H$202,H$222,$A226)</f>
-        <v>246.55750481814877</v>
+        <v>-25.274918834323856</v>
       </c>
       <c r="I226" t="s">
         <v>167</v>
@@ -7294,19 +7294,19 @@
       </c>
       <c r="E227" s="7">
         <f t="array" ref="E227">INDEX($D$191:$H$202,E$222,$A227)</f>
-        <v>364.74222496147917</v>
+        <v>400.86691587057004</v>
       </c>
       <c r="F227" s="7">
         <f t="array" ref="F227">INDEX($D$191:$H$202,F$222,$A227)</f>
-        <v>404.08189594623207</v>
+        <v>440.20658685532317</v>
       </c>
       <c r="G227" s="7">
         <f t="array" ref="G227">INDEX($D$191:$H$202,G$222,$A227)</f>
-        <v>407.71825958259569</v>
+        <v>116.57022321895955</v>
       </c>
       <c r="H227" s="7">
         <f t="array" ref="H227">INDEX($D$191:$H$202,H$222,$A227)</f>
-        <v>364.39293121044642</v>
+        <v>104.18313218078387</v>
       </c>
       <c r="I227" t="s">
         <v>166</v>
@@ -7352,19 +7352,19 @@
       </c>
       <c r="E230" s="7">
         <f t="array" ref="E230">INDEX($D$191:$H$202,E$229,$A230)</f>
-        <v>2275.8488340117592</v>
+        <v>2367.9179855269108</v>
       </c>
       <c r="F230" s="7">
         <f t="array" ref="F230">INDEX($D$191:$H$202,F$229,$A230)</f>
-        <v>2002.1573001357992</v>
+        <v>2094.2264516509508</v>
       </c>
       <c r="G230" s="7">
         <f t="array" ref="G230">INDEX($D$191:$H$202,G$229,$A230)</f>
-        <v>2005.7936637721632</v>
+        <v>2097.8628152873148</v>
       </c>
       <c r="H230" s="7">
         <f t="array" ref="H230">INDEX($D$191:$H$202,H$229,$A230)</f>
-        <v>1792.6521939280813</v>
+        <v>1874.9378095613156</v>
       </c>
       <c r="I230" t="s">
         <v>166</v>
@@ -7457,19 +7457,19 @@
       </c>
       <c r="E233" s="7">
         <f t="array" ref="E233">INDEX($D$191:$H$202,E$229,$A233)</f>
-        <v>232.6303275671697</v>
+        <v>260.12266323150538</v>
       </c>
       <c r="F233" s="7">
         <f t="array" ref="F233">INDEX($D$191:$H$202,F$229,$A233)</f>
-        <v>273.44952394456271</v>
+        <v>300.94185960889848</v>
       </c>
       <c r="G233" s="7">
         <f t="array" ref="G233">INDEX($D$191:$H$202,G$229,$A233)</f>
-        <v>277.0858875809264</v>
+        <v>-22.694504027465133</v>
       </c>
       <c r="H233" s="7">
         <f t="array" ref="H233">INDEX($D$191:$H$202,H$229,$A233)</f>
-        <v>247.64193508534254</v>
+        <v>-20.282920008050358</v>
       </c>
       <c r="I233" t="s">
         <v>167</v>
@@ -7492,19 +7492,19 @@
       </c>
       <c r="E234" s="7">
         <f t="array" ref="E234">INDEX($D$191:$H$202,E$229,$A234)</f>
-        <v>337.3335502392344</v>
+        <v>374.62471387559799</v>
       </c>
       <c r="F234" s="7">
         <f t="array" ref="F234">INDEX($D$191:$H$202,F$229,$A234)</f>
-        <v>377.92131247699666</v>
+        <v>415.21247611336014</v>
       </c>
       <c r="G234" s="7">
         <f t="array" ref="G234">INDEX($D$191:$H$202,G$229,$A234)</f>
-        <v>381.55767611336029</v>
+        <v>91.57611247699657</v>
       </c>
       <c r="H234" s="7">
         <f t="array" ref="H234">INDEX($D$191:$H$202,H$229,$A234)</f>
-        <v>341.01224744541361</v>
+        <v>81.844968357592705</v>
       </c>
       <c r="I234" t="s">
         <v>166</v>
@@ -7597,11 +7597,11 @@
       </c>
       <c r="E3" s="54">
         <f>Standardization!D121</f>
-        <v>7.1184803589743595</v>
+        <v>7.3439173589743589</v>
       </c>
       <c r="F3" s="54">
         <f>Standardization!D122</f>
-        <v>6.3245734390500221</v>
+        <v>6.5500104390500216</v>
       </c>
       <c r="H3" s="53" t="s">
         <v>171</v>
@@ -7619,11 +7619,11 @@
       </c>
       <c r="L3" s="54">
         <f>Standardization!H121</f>
-        <v>1.8130411186440678</v>
+        <v>1.9123840186440677</v>
       </c>
       <c r="M3" s="54">
         <f>Standardization!H122</f>
-        <v>1.9212252138521382</v>
+        <v>2.0205681138521387</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -7657,19 +7657,19 @@
       </c>
       <c r="J4" s="55">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="K4" s="55">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="L4" s="55">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="M4" s="55">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -7865,11 +7865,11 @@
       </c>
       <c r="E9" s="54">
         <f>(E3-E4) / E8 * 10^6</f>
-        <v>2053.4764562527325</v>
+        <v>2126.7424229991084</v>
       </c>
       <c r="F9" s="54">
         <f>(F3-F4) / F8 * 10^6</f>
-        <v>1795.4604340607473</v>
+        <v>1868.7264008071234</v>
       </c>
       <c r="H9" s="53" t="s">
         <v>178</v>
@@ -7879,19 +7879,19 @@
       </c>
       <c r="J9" s="54">
         <f>(J3-J4) / J8 * 10^6</f>
-        <v>49.366786946129317</v>
+        <v>-243.12898824489375</v>
       </c>
       <c r="K9" s="54">
         <f>(K3-K4) / K8 * 10^6</f>
-        <v>43.915679241251027</v>
+        <v>-248.58009594977204</v>
       </c>
       <c r="L9" s="54">
         <f>(L3-L4) / L8 * 10^6</f>
-        <v>329.23360810908645</v>
+        <v>69.023809079423657</v>
       </c>
       <c r="M9" s="54">
         <f>(M3-M4) / M8 * 10^6</f>
-        <v>364.39293121044642</v>
+        <v>104.18313218078387</v>
       </c>
     </row>
     <row r="12" spans="1:13">

--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Sherwin_2022_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Sherwin_2022_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{B84FD12B-CCB6-0543-A95D-92C612F77944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D21CA660-74B3-4DE0-9843-8378FB94577A}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -1094,7 +1094,7 @@
         </row>
         <row r="34">
           <cell r="C34">
-            <v>523</v>
+            <v>497</v>
           </cell>
         </row>
       </sheetData>
@@ -1442,9 +1442,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="C33" s="48">
         <f>[1]Inputs!C34</f>
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -1826,16 +1826,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:AJ234"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="62.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.09765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="15.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
@@ -1845,7 +1845,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="2:9" s="2" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="3" spans="2:9" s="2" customFormat="1" ht="33.9" customHeight="1">
       <c r="C3" s="2" t="s">
         <v>31</v>
       </c>
@@ -4568,11 +4568,11 @@
       </c>
       <c r="G106" s="21">
         <f>Inputs!$C$33</f>
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="H106" s="21">
         <f>Inputs!$C$33</f>
-        <v>523</v>
+        <v>497</v>
       </c>
     </row>
     <row r="107" spans="2:15">
@@ -4700,11 +4700,11 @@
       </c>
       <c r="G114" s="5">
         <f>G89/G105*G106</f>
-        <v>0.64530153846153837</v>
+        <v>0.61322153846153837</v>
       </c>
       <c r="H114" s="5">
         <f>H89/H105*H106</f>
-        <v>1.1558300000000001</v>
+        <v>1.0983700000000001</v>
       </c>
       <c r="I114" t="s">
         <v>21</v>
@@ -4728,11 +4728,11 @@
       </c>
       <c r="G115" s="5">
         <f>G102/G105*G106</f>
-        <v>0.12801430769230768</v>
+        <v>0.12165030769230768</v>
       </c>
       <c r="H115" s="5">
         <f>H102/H105*H106</f>
-        <v>5.2456900000000008E-2</v>
+        <v>4.9849100000000007E-2</v>
       </c>
       <c r="I115" t="s">
         <v>21</v>
@@ -4841,11 +4841,11 @@
       </c>
       <c r="G121" s="5">
         <f>G103+(G114-G89)+(G115-G102)+(G116-G80)</f>
-        <v>1.5141026258148629</v>
+        <v>1.4756586258148632</v>
       </c>
       <c r="H121" s="29">
         <f>H103+(H114-H89)+(H115-H102)+(H116-H80)</f>
-        <v>1.9123840186440677</v>
+        <v>1.852316218644068</v>
       </c>
     </row>
     <row r="122" spans="2:15" ht="17.100000000000001" customHeight="1" thickBot="1">
@@ -4869,11 +4869,11 @@
       </c>
       <c r="G122" s="32">
         <f>G103*G118+(G114-G89)+(G115-G102)+(G116-G80)</f>
-        <v>1.6222298956761492</v>
+        <v>1.583785895676149</v>
       </c>
       <c r="H122" s="33">
         <f>H103*H118+(H114-H89)+(H115-H102)+(H116-H80)</f>
-        <v>2.0205681138521387</v>
+        <v>1.9605003138521384</v>
       </c>
     </row>
     <row r="125" spans="2:15">
@@ -5611,11 +5611,11 @@
       </c>
       <c r="G152" s="21">
         <f>Inputs!$C$33</f>
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="H152" s="21">
         <f>Inputs!$C$33</f>
-        <v>523</v>
+        <v>497</v>
       </c>
     </row>
     <row r="154" spans="2:8">
@@ -5731,11 +5731,11 @@
       </c>
       <c r="G160" s="5">
         <f>G135/G151*G152</f>
-        <v>0.66984230769230779</v>
+        <v>0.6365423076923078</v>
       </c>
       <c r="H160" s="5">
         <f>H135/H151*H152</f>
-        <v>1.1851179999999999</v>
+        <v>1.1262019999999999</v>
       </c>
     </row>
     <row r="161" spans="2:9">
@@ -5756,11 +5756,11 @@
       </c>
       <c r="G161" s="5">
         <f>G148/G151*G152</f>
-        <v>0.24971238461538461</v>
+        <v>0.23729838461538463</v>
       </c>
       <c r="H161" s="5">
         <f>H148/H151*H152</f>
-        <v>6.2184699999999996E-2</v>
+        <v>5.9093299999999994E-2</v>
       </c>
     </row>
     <row r="162" spans="2:9">
@@ -5863,11 +5863,11 @@
       </c>
       <c r="G167" s="5">
         <f>G149+(G160-G135)+(G161-G148)+(G162-G126)</f>
-        <v>1.5253373238866399</v>
+        <v>1.4796233238866396</v>
       </c>
       <c r="H167" s="29">
         <f>H149+(H160-H135)+(H161-H148)+(H162-H126)</f>
-        <v>1.8402179631578945</v>
+        <v>1.7782105631578946</v>
       </c>
     </row>
     <row r="168" spans="2:9" ht="17.100000000000001" customHeight="1" thickBot="1">
@@ -5891,11 +5891,11 @@
       </c>
       <c r="G168" s="32">
         <f>G149*G164+(G160-G135)+(G161-G148)+(G162-G126)</f>
-        <v>1.6375901139244708</v>
+        <v>1.5918761139244706</v>
       </c>
       <c r="H168" s="33">
         <f>H149*H164+(H160-H135)+(H161-H148)+(H162-H126)</f>
-        <v>1.9518343093117405</v>
+        <v>1.8898269093117408</v>
       </c>
     </row>
     <row r="170" spans="2:9">
@@ -6130,11 +6130,11 @@
       </c>
       <c r="G182" s="4">
         <f>(G121-$C$173)/$C$172*1000</f>
-        <v>423.31004575085916</v>
+        <v>409.33040938722291</v>
       </c>
       <c r="H182" s="38">
         <f>(H121-$C$173)/$C$172*1000</f>
-        <v>568.13964314329735</v>
+        <v>546.29680677966121</v>
       </c>
     </row>
     <row r="183" spans="2:8">
@@ -6156,11 +6156,11 @@
       </c>
       <c r="G183" s="4">
         <f>(G167-$C$173)/$C$172*1000</f>
-        <v>427.39539050423275</v>
+        <v>410.77211777695993</v>
       </c>
       <c r="H183" s="38">
         <f>(H167-$C$173)/$C$172*1000</f>
-        <v>541.89744114832536</v>
+        <v>519.34929569377982</v>
       </c>
     </row>
     <row r="184" spans="2:8">
@@ -6184,11 +6184,11 @@
       </c>
       <c r="G184" s="4">
         <f>(G122-$C$173)/$C$172*1000</f>
-        <v>462.62905297314512</v>
+        <v>448.64941660950871</v>
       </c>
       <c r="H184" s="38">
         <f>(H122-$C$173)/$C$172*1000</f>
-        <v>607.47931412805042</v>
+        <v>585.63647776441394</v>
       </c>
     </row>
     <row r="185" spans="2:8">
@@ -6210,11 +6210,11 @@
       </c>
       <c r="G185" s="4">
         <f>(G168-$C$173)/$C$172*1000</f>
-        <v>468.21458688162579</v>
+        <v>451.59131415435297</v>
       </c>
       <c r="H185" s="38">
         <f>(H168-$C$173)/$C$172*1000</f>
-        <v>582.48520338608739</v>
+        <v>559.93705793154197</v>
       </c>
     </row>
     <row r="186" spans="2:8">
@@ -6238,11 +6238,11 @@
       </c>
       <c r="G186" s="4">
         <f>(G122-G$173)/$C$172*1000</f>
-        <v>-28.280037935945742</v>
+        <v>-42.259674299582151</v>
       </c>
       <c r="H186" s="38">
         <f>(H122-H$173)/$C$172*1000</f>
-        <v>116.57022321895955</v>
+        <v>94.727386855323076</v>
       </c>
     </row>
     <row r="187" spans="2:8">
@@ -6264,11 +6264,11 @@
       </c>
       <c r="G187" s="4">
         <f>(G168-G$173)/$C$172*1000</f>
-        <v>-22.694504027465133</v>
+        <v>-39.317776754737949</v>
       </c>
       <c r="H187" s="38">
         <f>(H168-H$173)/$C$172*1000</f>
-        <v>91.57611247699657</v>
+        <v>69.027967022451222</v>
       </c>
     </row>
     <row r="188" spans="2:8">
@@ -6292,11 +6292,11 @@
       </c>
       <c r="G188" s="7">
         <f>(G122-G$173)/$D$172*1000</f>
-        <v>-25.274918834323856</v>
+        <v>-37.769038369261338</v>
       </c>
       <c r="H188" s="40">
         <f>(H122-H$173)/$D$172*1000</f>
-        <v>104.18313218078387</v>
+        <v>84.661379152984495</v>
       </c>
     </row>
     <row r="189" spans="2:8" ht="17.100000000000001" customHeight="1" thickBot="1">
@@ -6318,11 +6318,11 @@
       </c>
       <c r="G189" s="42">
         <f>(G168-G$173)/$D$172*1000</f>
-        <v>-20.282920008050358</v>
+        <v>-35.139755415919808</v>
       </c>
       <c r="H189" s="43">
         <f>(H168-H$173)/$D$172*1000</f>
-        <v>81.844968357592705</v>
+        <v>61.692854434726307</v>
       </c>
     </row>
     <row r="190" spans="2:8" ht="17.100000000000001" customHeight="1" thickBot="1">
@@ -6463,11 +6463,11 @@
       </c>
       <c r="G195" s="4">
         <f>(G121-$C$174)/$C$172*1000</f>
-        <v>256.03731847813197</v>
+        <v>242.05768211449569</v>
       </c>
       <c r="H195" s="38">
         <f>(H121-$C$174)/$C$172*1000</f>
-        <v>400.86691587057004</v>
+        <v>379.02407950693379</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -6489,11 +6489,11 @@
       </c>
       <c r="G196" s="4">
         <f>(G167-$C$174)/$C$172*1000</f>
-        <v>260.12266323150538</v>
+        <v>243.49939050423259</v>
       </c>
       <c r="H196" s="38">
         <f>(H167-$C$174)/$C$172*1000</f>
-        <v>374.62471387559799</v>
+        <v>352.07656842105257</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -6517,11 +6517,11 @@
       </c>
       <c r="G197" s="4">
         <f>(G122-$C$174)/$C$172*1000</f>
-        <v>295.35632570041787</v>
+        <v>281.37668933678145</v>
       </c>
       <c r="H197" s="38">
         <f>(H122-$C$174)/$C$172*1000</f>
-        <v>440.20658685532317</v>
+        <v>418.36375049168669</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -6543,11 +6543,11 @@
       </c>
       <c r="G198" s="4">
         <f>(G168-$C$174)/$C$172*1000</f>
-        <v>300.94185960889848</v>
+        <v>284.31858688162566</v>
       </c>
       <c r="H198" s="38">
         <f>(H168-$C$174)/$C$172*1000</f>
-        <v>415.21247611336014</v>
+        <v>392.66433065881483</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -6571,11 +6571,11 @@
       </c>
       <c r="G199" s="4">
         <f>(G122-G$173)/$C$172*1000</f>
-        <v>-28.280037935945742</v>
+        <v>-42.259674299582151</v>
       </c>
       <c r="H199" s="38">
         <f>(H122-H$173)/$C$172*1000</f>
-        <v>116.57022321895955</v>
+        <v>94.727386855323076</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -6597,11 +6597,11 @@
       </c>
       <c r="G200" s="4">
         <f>(G168-G$173)/$C$172*1000</f>
-        <v>-22.694504027465133</v>
+        <v>-39.317776754737949</v>
       </c>
       <c r="H200" s="38">
         <f>(H168-H$173)/$C$172*1000</f>
-        <v>91.57611247699657</v>
+        <v>69.027967022451222</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -6625,11 +6625,11 @@
       </c>
       <c r="G201" s="7">
         <f>(G122-G$173)/$D$172*1000</f>
-        <v>-25.274918834323856</v>
+        <v>-37.769038369261338</v>
       </c>
       <c r="H201" s="40">
         <f>(H122-H$173)/$D$172*1000</f>
-        <v>104.18313218078387</v>
+        <v>84.661379152984495</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="17.100000000000001" customHeight="1" thickBot="1">
@@ -6651,11 +6651,11 @@
       </c>
       <c r="G202" s="42">
         <f>(G168-G$173)/$D$172*1000</f>
-        <v>-20.282920008050358</v>
+        <v>-35.139755415919808</v>
       </c>
       <c r="H202" s="43">
         <f>(H168-H$173)/$D$172*1000</f>
-        <v>81.844968357592705</v>
+        <v>61.692854434726307</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -6854,19 +6854,19 @@
       </c>
       <c r="E211" s="7">
         <f t="array" ref="E211">INDEX($D$178:$H$189,E$206,$A211)</f>
-        <v>423.31004575085916</v>
+        <v>409.33040938722291</v>
       </c>
       <c r="F211" s="7">
         <f t="array" ref="F211">INDEX($D$178:$H$189,F$206,$A211)</f>
-        <v>462.62905297314512</v>
+        <v>448.64941660950871</v>
       </c>
       <c r="G211" s="7">
         <f t="array" ref="G211">INDEX($D$178:$H$189,G$206,$A211)</f>
-        <v>-28.280037935945742</v>
+        <v>-42.259674299582151</v>
       </c>
       <c r="H211" s="7">
         <f t="array" ref="H211">INDEX($D$178:$H$189,H$206,$A211)</f>
-        <v>-25.274918834323856</v>
+        <v>-37.769038369261338</v>
       </c>
       <c r="I211" t="s">
         <v>167</v>
@@ -6889,19 +6889,19 @@
       </c>
       <c r="E212" s="7">
         <f t="array" ref="E212">INDEX($D$178:$H$189,E$206,$A212)</f>
-        <v>568.13964314329735</v>
+        <v>546.29680677966121</v>
       </c>
       <c r="F212" s="7">
         <f t="array" ref="F212">INDEX($D$178:$H$189,F$206,$A212)</f>
-        <v>607.47931412805042</v>
+        <v>585.63647776441394</v>
       </c>
       <c r="G212" s="7">
         <f t="array" ref="G212">INDEX($D$178:$H$189,G$206,$A212)</f>
-        <v>116.57022321895955</v>
+        <v>94.727386855323076</v>
       </c>
       <c r="H212" s="7">
         <f t="array" ref="H212">INDEX($D$178:$H$189,H$206,$A212)</f>
-        <v>104.18313218078387</v>
+        <v>84.661379152984495</v>
       </c>
       <c r="I212" t="s">
         <v>166</v>
@@ -7061,19 +7061,19 @@
       </c>
       <c r="E219" s="7">
         <f t="array" ref="E219">INDEX($D$178:$H$189,E$214,$A219)</f>
-        <v>427.39539050423275</v>
+        <v>410.77211777695993</v>
       </c>
       <c r="F219" s="7">
         <f t="array" ref="F219">INDEX($D$178:$H$189,F$214,$A219)</f>
-        <v>468.21458688162579</v>
+        <v>451.59131415435297</v>
       </c>
       <c r="G219" s="7">
         <f t="array" ref="G219">INDEX($D$178:$H$189,G$214,$A219)</f>
-        <v>-22.694504027465133</v>
+        <v>-39.317776754737949</v>
       </c>
       <c r="H219" s="7">
         <f t="array" ref="H219">INDEX($D$178:$H$189,H$214,$A219)</f>
-        <v>-20.282920008050358</v>
+        <v>-35.139755415919808</v>
       </c>
       <c r="I219" t="s">
         <v>167</v>
@@ -7096,19 +7096,19 @@
       </c>
       <c r="E220" s="7">
         <f t="array" ref="E220">INDEX($D$178:$H$189,E$214,$A220)</f>
-        <v>541.89744114832536</v>
+        <v>519.34929569377982</v>
       </c>
       <c r="F220" s="7">
         <f t="array" ref="F220">INDEX($D$178:$H$189,F$214,$A220)</f>
-        <v>582.48520338608739</v>
+        <v>559.93705793154197</v>
       </c>
       <c r="G220" s="7">
         <f t="array" ref="G220">INDEX($D$178:$H$189,G$214,$A220)</f>
-        <v>91.57611247699657</v>
+        <v>69.027967022451222</v>
       </c>
       <c r="H220" s="7">
         <f t="array" ref="H220">INDEX($D$178:$H$189,H$214,$A220)</f>
-        <v>81.844968357592705</v>
+        <v>61.692854434726307</v>
       </c>
       <c r="I220" t="s">
         <v>166</v>
@@ -7259,19 +7259,19 @@
       </c>
       <c r="E226" s="7">
         <f t="array" ref="E226">INDEX($D$191:$H$202,E$222,$A226)</f>
-        <v>256.03731847813197</v>
+        <v>242.05768211449569</v>
       </c>
       <c r="F226" s="7">
         <f t="array" ref="F226">INDEX($D$191:$H$202,F$222,$A226)</f>
-        <v>295.35632570041787</v>
+        <v>281.37668933678145</v>
       </c>
       <c r="G226" s="7">
         <f t="array" ref="G226">INDEX($D$191:$H$202,G$222,$A226)</f>
-        <v>-28.280037935945742</v>
+        <v>-42.259674299582151</v>
       </c>
       <c r="H226" s="7">
         <f t="array" ref="H226">INDEX($D$191:$H$202,H$222,$A226)</f>
-        <v>-25.274918834323856</v>
+        <v>-37.769038369261338</v>
       </c>
       <c r="I226" t="s">
         <v>167</v>
@@ -7294,19 +7294,19 @@
       </c>
       <c r="E227" s="7">
         <f t="array" ref="E227">INDEX($D$191:$H$202,E$222,$A227)</f>
-        <v>400.86691587057004</v>
+        <v>379.02407950693379</v>
       </c>
       <c r="F227" s="7">
         <f t="array" ref="F227">INDEX($D$191:$H$202,F$222,$A227)</f>
-        <v>440.20658685532317</v>
+        <v>418.36375049168669</v>
       </c>
       <c r="G227" s="7">
         <f t="array" ref="G227">INDEX($D$191:$H$202,G$222,$A227)</f>
-        <v>116.57022321895955</v>
+        <v>94.727386855323076</v>
       </c>
       <c r="H227" s="7">
         <f t="array" ref="H227">INDEX($D$191:$H$202,H$222,$A227)</f>
-        <v>104.18313218078387</v>
+        <v>84.661379152984495</v>
       </c>
       <c r="I227" t="s">
         <v>166</v>
@@ -7457,19 +7457,19 @@
       </c>
       <c r="E233" s="7">
         <f t="array" ref="E233">INDEX($D$191:$H$202,E$229,$A233)</f>
-        <v>260.12266323150538</v>
+        <v>243.49939050423259</v>
       </c>
       <c r="F233" s="7">
         <f t="array" ref="F233">INDEX($D$191:$H$202,F$229,$A233)</f>
-        <v>300.94185960889848</v>
+        <v>284.31858688162566</v>
       </c>
       <c r="G233" s="7">
         <f t="array" ref="G233">INDEX($D$191:$H$202,G$229,$A233)</f>
-        <v>-22.694504027465133</v>
+        <v>-39.317776754737949</v>
       </c>
       <c r="H233" s="7">
         <f t="array" ref="H233">INDEX($D$191:$H$202,H$229,$A233)</f>
-        <v>-20.282920008050358</v>
+        <v>-35.139755415919808</v>
       </c>
       <c r="I233" t="s">
         <v>167</v>
@@ -7492,19 +7492,19 @@
       </c>
       <c r="E234" s="7">
         <f t="array" ref="E234">INDEX($D$191:$H$202,E$229,$A234)</f>
-        <v>374.62471387559799</v>
+        <v>352.07656842105257</v>
       </c>
       <c r="F234" s="7">
         <f t="array" ref="F234">INDEX($D$191:$H$202,F$229,$A234)</f>
-        <v>415.21247611336014</v>
+        <v>392.66433065881483</v>
       </c>
       <c r="G234" s="7">
         <f t="array" ref="G234">INDEX($D$191:$H$202,G$229,$A234)</f>
-        <v>91.57611247699657</v>
+        <v>69.027967022451222</v>
       </c>
       <c r="H234" s="7">
         <f t="array" ref="H234">INDEX($D$191:$H$202,H$229,$A234)</f>
-        <v>81.844968357592705</v>
+        <v>61.692854434726307</v>
       </c>
       <c r="I234" t="s">
         <v>166</v>
@@ -7518,10 +7518,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="6" max="6" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -7619,11 +7619,11 @@
       </c>
       <c r="L3" s="54">
         <f>Standardization!H121</f>
-        <v>1.9123840186440677</v>
+        <v>1.852316218644068</v>
       </c>
       <c r="M3" s="54">
         <f>Standardization!H122</f>
-        <v>2.0205681138521387</v>
+        <v>1.9605003138521384</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -7887,11 +7887,11 @@
       </c>
       <c r="L9" s="54">
         <f>(L3-L4) / L8 * 10^6</f>
-        <v>69.023809079423657</v>
+        <v>49.502056051624507</v>
       </c>
       <c r="M9" s="54">
         <f>(M3-M4) / M8 * 10^6</f>
-        <v>104.18313218078387</v>
+        <v>84.661379152984495</v>
       </c>
     </row>
     <row r="12" spans="1:13">
